--- a/docs/harness/wirelist/EngineRoom-C-pinouts.xlsx
+++ b/docs/harness/wirelist/EngineRoom-C-pinouts.xlsx
@@ -975,7 +975,7 @@
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall) pin 44</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall) pin 84</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall) pin 56</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall) pin 85</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Bulkhead BH-A (DRB102, RH firewall) pin 42</t>
+          <t>Bulkhead BH-A (DRB102, RH firewall) pin 83</t>
         </is>
       </c>
     </row>
